--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_05_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_05_19_Cau.xlsx
@@ -689,7 +689,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Overview, Engineering detail.</t>
+          <t>Thiết kế bảng điều khiển trực quan hiệu quả theo nguyên lý phân cấp nhận thức: Bắt đầu từ màn hình tổng quan mức cao (Overview) → xem chi tiết kỹ thuật (Detail) → cho phép đi sâu vào từng vết sự cố (Drill-down).</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Named panel profile, Traffic.</t>
+          <t>Bảng điều khiển hiện tại vi phạm nghiêm trọng yêu cầu đặc tả vì thiếu cả bốn liên kết chỉ số trọng yếu: TTFT P95, chi phí tác vụ P95, tỷ lệ lỗi công cụ và độ tin cậy nội dung (groundedness).</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Versioned definition, Code review.</t>
+          <t>Để bảo đảm tính nhất quán và khả năng tái lập giữa các môi trường, toàn bộ cấu hình bảng điều khiển phải được quản lý dưới dạng mã nguồn (Dashboard-as-Code), có quy trình kiểm thử và review trước khi triển khai.</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: User-visible symptom, Cause candidate.</t>
+          <t>Nguyên tắc phát cảnh báo SRE: Chỉ phát cảnh báo khẩn cấp (page on-call) khi có triệu chứng ảnh hưởng trực tiếp đến người dùng (breach SLO/latency); các chỉ số tài nguyên như GPU 95% chỉ dùng để chẩn đoán nguyên nhân.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Condition/duration, Severity.</t>
+          <t>Cảnh báo có thể hành động được (actionable alert) bắt buộc phải cung cấp đầy đủ: Điều kiện kích hoạt, thời gian duy trì, mức độ ảnh hưởng, liên kết bằng chứng và quy trình/người chịu trách nhiệm xử lý.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_05_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_05_19_Cau.xlsx
@@ -720,10 +720,30 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Overview, Engineering detail.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Overview, Engineering detail.</t>
+- 1.0đ: Thiết kế Tầng 1 phục vụ Product/Executive với các chỉ số nghiệp vụ và chi phí phù hợp.
+- 1.0đ: Thiết kế Tầng 2 phục vụ On-Call SRE với các chỉ số kỹ thuật RED/SLO và phân phối độ trễ.
+- 1.0đ: Thiết kế Tầng 3 phục vụ Deep Debug với trace waterfall và structured event logs.
+- 1.0đ: Thiết lập cơ chế chuyển giao (handoff/drilldown) mạch lạc qua Dashboard Links và Trace Exemplars.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Bảng điều khiển Ba tầng (Three-layered Dashboard Architecture) và Cơ chế Handoff:
+1. **Tầng 1: Executive &amp; Product Layer (Tổng quan Chất lượng &amp; Kinh doanh)**:
+- Đối tượng: Product Manager, Business Owner, C-Level.
+- Nội dung hiển thị: Tỷ lệ hoàn thành tác vụ (`task_completion_rate`), điểm chất lượng trung bình (`average_faithfulness`), chi phí trên mỗi tác vụ thành công (`cost_per_task`), và khối lượng người dùng hoạt động (DAU/MAU).
+- Dạng biểu đồ: KPI Stat Cards, biểu đồ tròn phân bổ chi phí theo feature, đồ thị xu hướng tuần.
+2. **Tầng 2: Service &amp; On-Call SRE Layer (Vận hành &amp; Độ tin cậy Kỹ thuật)**:
+- Đối tượng: SRE, DevOps, Kỹ sư On-call trực chiến.
+- Nội dung hiển thị: Tứ trụ RED/USE: HTTP 5xx error rate, P95/P99 latency, model timeout rate, tool call failure rate, và error budget burn rate.
+- Dạng biểu đồ: Time-series line graphs, heatmap phân phối độ trễ, bảng xếp hạng các tenant bị lỗi nhiều nhất.
+3. **Tầng 3: Deep Diagnostic &amp; Request Trace Layer (Đào sâu gỡ lỗi chi tiết)**:
+- Đối tượng: Kỹ sư phần mềm phát triển Agent khi cần fix bug.
+- Nội dung hiển thị: Chi tiết từng request cụ thể: Trace waterfall hiển thị từng span (prompt planning, tool retries, token usage), structured log messages, và input/output arguments đã được khử khuẩn.
+4. **Cơ chế Handoff liền mạch giữa các tầng (Seamless Drilldown)**:
+- Từ Tầng 1 sang Tầng 2: Khi Product Manager thấy chỉ số `task_completion_rate` giảm, bấm vào widget sẽ chuyển hướng (Dashboard Link) sang Tầng 2 với bộ lọc tự động gán theo `feature_name` và khoảng thời gian xảy ra sụt giảm.
+- Từ Tầng 2 sang Tầng 3: Khi kỹ sư On-call thấy đột biến lỗi trên đồ thị time-series ở Tầng 2, nhấp chuột vào điểm lỗi (sử dụng Grafana Exemplar) sẽ mở trực tiếp biểu đồ Trace Waterfall của đúng `trace_id` bị lỗi đó ở Tầng 3.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Bảng điều khiển Phân tầng (Layered Dashboard Design): Không thể nhồi nhét tất cả thông tin vào một màn hình duy nhất. Một bảng điều khiển hiệu quả phải phục vụ đúng nhu cầu ra quyết định của từng nhóm đối tượng: từ chiến lược kinh doanh (Tầng 1), đến cảnh báo vận hành kỹ thuật (Tầng 2), và công cụ gỡ lỗi chi tiết (Tầng 3). Sự kết hợp giữa Dashboard Links và Trace Exemplars giúp rút ngắn thời gian điều tra từ tổng quan vĩ mô xuống vi mô chỉ bằng một cú nhấp chuột.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Grafana Dashboard Best Practices (https://grafana.com/docs/grafana/latest/dashboards/build-dashboards/best-practices/) &amp; Google SRE Book</t>
         </is>
       </c>
     </row>
@@ -802,10 +822,27 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Named panel profile, Traffic.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Named panel profile, Traffic.</t>
+- 1.0đ: Ánh xạ chuẩn xác các panels cho Profile API Service (Rate, Error %, Latency P95) kèm công thức PromQL chuẩn.
+- 1.0đ: Ánh xạ chuẩn xác các panels cho Profile AI Task Quality (Groundedness, Regenerate rate, Cost/task).
+- 1.0đ: Chỉ ra và phân tích bản chất của Binding Sai 1 (đánh tráo HTTP 200 với chất lượng câu trả lời AI).
+- 1.0đ: Chỉ ra và phân tích bản chất của Binding Sai 2 (dùng average latency che giấu tail lag thay vì percentiles).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Ánh xạ Panel sang Event / Field / Aggregation cho Hai Profile Dashboard:
+- **Profile 1: API Service Dashboard (Góc nhìn Kỹ thuật Hạ tầng)**:
+  + Panel 1 - Request Rate: Event: `http_requests_total`, Aggregation: `sum(rate(http_requests_total[5m])) by (endpoint)`.
+  + Panel 2 - Error Rate: Event: `http_requests_total{status=~'5..'}`, Aggregation: `sum(rate(http_requests_total{status=~'5..'}[5m])) / sum(rate(http_requests_total[5m])) * 100`.
+  + Panel 3 - Latency Percentiles: Event: `http_request_duration_seconds_bucket`, Aggregation: `histogram_quantile(0.95, sum(rate(http_request_duration_seconds_bucket[5m])) by (le))`.
+- **Profile 2: AI Task Quality Dashboard (Góc nhìn Chất lượng Nghiệp vụ AI)**:
+  + Panel 1 - Groundedness / Faithfulness Trend: Event: `eval_score_event`, Field: `faithfulness_score`, Aggregation: `avg_over_time(llm_eval_faithfulness_score[1h]) by (model_version)`.
+  + Panel 2 - User Regeneration &amp; Thumbs-Down Ratio: Event: `user_feedback_event`, Aggregation: `sum(rate(feedback_regenerate_total[1h])) / sum(rate(agent_tasks_total[1h]))`.
+  + Panel 3 - Token Cost per Resolved Task: Event: `task_completed_event`, Aggregation: `sum(rate(task_cost_usd_total[1d])) / sum(rate(successful_tasks_total[1d]))`.
+2. Nhận diện và Báo cáo Binding Sai (Mismatched / Erroneous Bindings):
+- **Binding Sai 1**: Đưa biểu đồ `HTTP 200 Success Rate` vào dashboard AI Quality và kết luận 'Chất lượng câu trả lời tốt'. Đây là binding sai bản chất vì HTTP 200 chỉ chứng minh mạng thông suốt, không chứng minh câu trả lời đúng sự thật (hallucination blind spot).
+- **Binding Sai 2**: Sử dụng hàm `avg(latency)` cho API Service thay vì Percentile (`histogram_quantile`). Hàm trung bình che giấu tail lag nghiêm trọng của người dùng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sự phân biệt giữa API Service Health và AI Task Quality là nguyên tắc căn bản của AI Observability. Một hệ thống API có thể đạt 99.99% uptime với độ trễ cực nhanh nhưng chất lượng câu trả lời sinh ra hoàn toàn vô nghĩa hoặc vi phạm đạo đức. Việc gán ghép nhầm các chỉ số hạ tầng (như HTTP status) làm thước đo cho chất lượng nội dung AI là lỗi kiến trúc nguy hiểm cần được loại bỏ trên dashboard.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Arize AI: LLM Evaluation Metrics in Production &amp; Datadog AI Observability Best Practices</t>
         </is>
       </c>
     </row>
@@ -888,10 +925,25 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Time series, Single-value stat.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Time series, Single-value stat.</t>
+- 1.0đ: Chọn đúng Stacked Bar Chart cho so sánh chi phí theo model và lập luận phân rã cấu trúc token.
+- 1.0đ: Chọn đúng Time-series Line Graph cho xu hướng lỗi theo thời gian kèm ngưỡng threshold cảnh báo trực quan.
+- 1.0đ: Chọn đúng Gantt/Trace Waterfall Panel cho phân tích request đơn lẻ và lý giải khả năng nhìn critical path.
+- 1.0đ: Nêu rõ cơ sở lý luận kỹ thuật vì sao các dạng biểu đồ khác không phù hợp cho từng bài toán.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Lựa chọn Định dạng Panel (Panel Form Selection) tối ưu cho từng bài toán trực quan hóa:
+1. **Bài toán 1: So sánh Chi phí theo Mô hình (Comparing Cost across Models)**:
+- **Dạng Panel tối ưu**: **Stacked Bar Chart (Biểu đồ Cột Chồng) hoặc Horizontal Bar Gauge**.
+- **Lý do kỹ thuật**: Cung cấp khả năng so sánh tuyệt đối và tương đối rõ ràng giữa các danh mục rời rạc (`gpt-4o`, `claude-3-5-sonnet`, `llama-3-70b`). Cột chồng cho phép bóc tách cấu trúc chi phí (chi phí prompt tokens vs completion tokens vs cached tokens) của từng model. Tránh dùng Pie chart nếu có nhiều hơn 3-4 model vì khó so sánh góc nhìn.
+2. **Bài toán 2: Xu hướng Lỗi theo Thời gian (Error Trend over Time)**:
+- **Dạng Panel tối ưu**: **Time-series Line Graph kèm Threshold Bands (Đồ thị Đường theo Chuỗi Thời gian)**.
+- **Lý do kỹ thuật**: Trục hoành là thời gian liên tục, trục tung là tỷ lệ lỗi (`error_rate %`). Cho phép người vận hành nhìn thấy ngay lập tức các xung đột biến (spikes), xu hướng thoái hóa dần dần (gradual degradation), hoặc tính chu kỳ (seasonality). Các dải màu cảnh báo (Thresholds: Vàng &gt; 1%, Đỏ &gt; 5%) giúp nhận diện vi phạm trong tích tắc.
+3. **Bài toán 3: Phân tích Chi tiết Lược đồ Thực thi một Request (Trace Waterfall of a Single Request)**:
+- **Dạng Panel tối ưu**: **Gantt Chart / Distributed Trace Waterfall Panel**.
+- **Lý do kỹ thuật**: Trực quan hóa cấu trúc cây phân cấp (hierarchy) và trục thời gian tuyến tính của các spans. Giúp kỹ sư nhìn thấy ngay lập tức span nào chạy tuần tự, span nào chạy song song (fan-out), và span nào chiếm thời gian dài nhất trên đường găng (critical path).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Trực quan hóa Dữ liệu trong SRE (Visualization Form follows Function): Mỗi loại dữ liệu có một hình thức biểu diễn tối ưu. Dữ liệu danh mục so sánh tĩnh thuộc về Bar Charts; dữ liệu diễn tiến theo thời gian thuộc về Time-series Lines; và dữ liệu phân tán có quan hệ cha-con phụ thuộc về mặt thời gian bắt buộc phải sử dụng Gantt/Waterfall Tracing. Chọn sai dạng panel (ví dụ: dùng Pie chart cho chuỗi thời gian, hoặc dùng bảng text cho trace) sẽ làm chậm đáng kể tốc độ phản ứng sự cố của kỹ sư.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Stephen Few: Show Me the Numbers &amp; Grafana Panels Documentation (https://grafana.com/docs/grafana/latest/panels-visualizations/)</t>
         </is>
       </c>
     </row>
@@ -970,10 +1022,25 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Time range, Unit.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Time range, Unit.</t>
+- 1.0đ: Chuẩn hóa tiêu đề ngữ cảnh rõ ràng và bắt buộc có đơn vị đo lường trên trục tọa độ.
+- 1.0đ: Thiết lập hệ thống phân màu ngưỡng trực quan (Green/Yellow/Red thresholds) nhận diện tức thì.
+- 1.0đ: Tích hợp đường cơ sở đối chiếu lịch sử (offset baseline comparison) phân biệt biến động bình thường vs dị thường.
+- 1.0đ: Cung cấp tài liệu hướng dẫn ngữ cảnh (description tooltip) và đường dẫn runbook hành động.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế lại Hợp đồng Panel Bảng điều khiển (Revised Operational Panel Contract) để người ngoài đội ngũ nhận biết dị thường trong 30 giây:
+1. **Tiêu đề Rõ ràng &amp; Đơn vị Bắt buộc (Explicit Title &amp; Unit Specification)**:
+- Thay vì tiêu đề mơ hồ 'Latency' hay 'Queue', đổi thành: `[Route: /chat] Thời gian Phản hồi P95 (giây)` và `[GPU Cluster 01] Độ sâu Hàng đợi Chờ Xử lý (số request)`.
+- Hiển thị rõ ràng đơn vị đo lường (ms, s, req/s, %, USD) trên cả trục tung (Y-axis) và tooltip khi rê chuột.
+2. **Dải Màu Ngưỡng Trực quan (Color-coded Thresholds)**:
+- Thiết lập quy tắc đổi màu theo trạng thái SRE: Xanh lục (&lt; 2s - Bình thường), Vàng (2s - 4s - Cảnh báo Warning), Đỏ rực (&gt; 4s - Vi phạm SLO/Critical Alert). Người xem lướt qua màn hình trong 3 giây là phát hiện ngay màu đỏ bất thường.
+3. **Đường Cơ sở Đối chiếu Lịch sử (Baseline Comparison Overlay)**:
+- Vẽ một đường nét đứt mờ biểu diễn dữ liệu cùng giờ tuần trước (`offset 7d`) hoặc giá trị trung bình 30 ngày. Giúp người ngoài nhận ra ngay: mức tải 500 req/s lúc 10h sáng là bình thường (vì tuần trước cũng 500 req/s) hay là dị thường đột biến.
+4. **Mô tả Hướng dẫn Ngay tại Panel (Description Tooltip &amp; Runbook Link)**:
+- Đính kèm biểu tượng `(i)` chứa nội dung giải thích: 'Panel này đo gì? Nếu vượt ngưỡng đỏ &gt; 4s, báo cho ai và mở runbook nào?'. Kèm đường link thẳng tới runbook xử lý sự cố.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc 30 Giây trong SRE (The 30-Second Dashboard Rule): Khi xảy ra sự cố lớn, kỹ sư trực ca (on-call) hoặc chỉ huy sự cố (Incident Commander) thường không phải là người trực tiếp viết code tính năng đó. Một panel không có đơn vị, không có ngưỡng đỏ và không có dữ liệu so sánh tuần trước sẽ biến thành một câu đố đánh đố người xem. Tiêu đề rõ ràng, dải màu chuẩn hóa và đường so sánh lịch sử giúp bất kỳ ai cũng có thể đọc vị được hệ thống trong tích tắc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Grafana Dashboard Design Guide: Make Dashboards Easy to Understand (https://grafana.com/docs/grafana/latest/dashboards/build-dashboards/best-practices/) &amp; Google SRE Workbook</t>
         </is>
       </c>
     </row>
@@ -1052,10 +1119,28 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Versioned definition, Code review.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Versioned definition, Code review.</t>
+- 1.0đ: Thiết lập mô hình Dashboard-as-Code lưu trữ trong Git, khóa quyền chỉnh sửa tùy tiện trên Web UI.
+- 1.0đ: Thiết kế quy trình CI tự động kiểm định cú pháp và tính hợp lệ của câu truy vấn PromQL.
+- 1.0đ: Xây dựng cơ chế kiểm thử trực quan trên môi trường staging trước khi triển khai sản xuất.
+- 1.0đ: Định nghĩa quy trình hoàn nguyên tức thì (git revert / automated sync) khôi phục phiên bản cũ an toàn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Quy trình Dashboard-as-Code (DaC) đảm bảo Thay đổi, Kiểm định và Hoàn nguyên (Change, Validation, Rollback Path):
+1. **Quản lý Phiên bản qua Mã nguồn (Version-controlled Source of Truth)**:
+- Toàn bộ cấu trúc Dashboard (Panels, PromQL queries, thresholds, alert rules) được định nghĩa dưới dạng mã (Terraform, Grafana JSONnet, hoặc Declarative YAML/JSON) và lưu trữ trong Git repository (`/dashboards/chat-service.json`).
+- Nghiêm cấm chỉnh sửa trực tiếp trên giao diện đồ họa (UI edit freeze trên production Grafana; bật chế độ `read_only` cho người dùng).
+2. **Quy trình Thay đổi &amp; Kiểm định CI/CD (Change &amp; Validation Pipeline)**:
+- Khi cần thay đổi metric nguồn hoặc ngưỡng threshold: Kỹ sư tạo Git Pull Request (PR) mô tả rõ lý do kỹ thuật.
+- **CI Automated Validation Suite**:
+  + `linter`: Kiểm tra cú pháp JSON/YAML và tuân thủ chuẩn đặt tên.
+  + `promql_validator`: Kiểm tra tính hợp lệ của câu truy vấn PromQL mới đối với Prometheus server (ngăn chặn syntax error hoặc query quá nặng làm sập TSDB).
+  + `preview_deployment`: Sinh bản xem trước (ephemeral preview dashboard) trên môi trường Staging để team review trực quan trước khi merge.
+3. **Cơ chế Hoàn nguyên Tức thì (Instant Rollback Path)**:
+- Nếu sau khi apply thay đổi, dashboard mới bị lỗi hoặc hiển thị sai số liệu trong ca trực: Kỹ sư chỉ cần thực hiện lệnh `git revert &lt;commit_hash&gt;` và đẩy lên nhánh main.
+- CI/CD pipeline tự động đồng bộ (ArgoCD / Terraform apply) đưa dashboard trên production trở về phiên bản ổn định trước đó trong vòng dưới 60 giây.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Dashboard-as-Code (DaC): Bảng điều khiển giám sát là tài sản kỹ thuật quan trọng của hệ thống. Nếu sửa tay trên web UI, thay đổi không được ghi vết, không có ai review, và khi xảy ra lỗi thì không có cách nào khôi phục lại trạng thái cũ. Đưa Dashboard vào quy trình GitOps với CI validation và khả năng `git revert` bảo đảm tính tái lập (reproducibility), minh bạch và an toàn tuyệt đối.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Grafana as Code with Terraform &amp; Grizzly (https://grafana.com/docs/grafana/latest/administration/dashboard-management/dashboard-as-code/) &amp; Google SRE Workbook</t>
         </is>
       </c>
     </row>
@@ -1134,10 +1219,28 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra User-visible symptom, Cause candidate.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra User-visible symptom, Cause candidate.</t>
+- 1.0đ: Phân định rạch ròi giữa Triệu chứng ảnh hưởng người dùng (P95 latency) và Nguyên nhân hạ tầng (queue saturation).
+- 1.0đ: Thiết lập quy tắc PAGE khẩn cấp chỉ kích hoạt khi triệu chứng thực sự vi phạm SLO có nguy cơ tổn thất cao.
+- 1.0đ: Thiết lập quy tắc WARNING/Ticket gửi Slack cho chỉ số bão hòa hàng đợi khi người dùng chưa bị ảnh hưởng.
+- 1.0đ: Lập luận chặt chẽ về việc phòng chống kiệt sức cảnh báo (Alert Fatigue Prevention).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Phân tách Cảnh báo Triệu chứng vs Nguyên nhân (Symptom-Cause Alert Separation) và Quy tắc Page / Warning:
+1. **Phân định Bản chất Triệu chứng vs Nguyên nhân**:
+- **Symptom (Triệu chứng vi phạm SLO)**: Độ trễ P95 của người dùng vượt ngưỡng cam kết (`P95 latency &gt; 3s`). Đây là nỗi đau thực sự của người dùng (user pain), trực tiếp đe dọa thỏa thuận dịch vụ.
+- **Cause (Nguyên nhân / Điềm báo)**: Hàng đợi bị ứ đọng (`queue saturation &gt; 80%`). Đây là chỉ số tài nguyên nội bộ, có thể báo trước sự cố độ trễ nhưng đôi khi chỉ là xung tải tạm thời và tự hồi phục sau vài giây.
+2. **Quy tắc Phân định Cảnh báo Khẩn (PAGE) vs Cảnh báo Chờ (WARNING)**:
+- **Quy tắc Cảnh báo Khẩn (PAGE - Đánh thức người trực đêm)**:
+  + **Chỉ áp dụng cho Triệu chứng ảnh hưởng trực tiếp đến người dùng**:
+    `histogram_quantile(0.95, rate(request_duration_seconds_bucket[5m])) &gt; 3s` duy trì liên tục trong 5 phút VÀ burn rate của error budget &gt; 14x.
+  + Hành động: Bắn PagerDuty/Opsgenie ngay lập tức để kỹ sư can thiệp khẩn cấp.
+- **Quy tắc Cảnh báo Không Khẩn (WARNING / TICKET - Không đánh thức đêm)**:
+  + **Áp dụng cho Nguyên nhân tiềm ẩn và tài nguyên bão hòa tạm thời**:
+    `inference_queue_depth &gt; 100` trong 10 phút nhưng P95 latency của người dùng VẪN ĐẠT SLO.
+  + Hành động: Gửi thông báo vào kênh Slack `#alerts-warning` hoặc tự động tạo ticket Jira để kỹ sư rà soát trong giờ hành chính. Tuyệt đối không rung chuông PagerDuty đánh thức on-call khi người dùng chưa chịu ảnh hưởng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Vàng trong SRE (Symptom-based Alerting vs Cause-based Alerts): Cảnh báo đánh thức kỹ sư on-call chỉ được kích hoạt khi có 'nỗi đau thực tế của khách hàng' (Symptom/SLO Breach). Nếu đặt cảnh báo khẩn cho mọi nguyên nhân (như queue saturation, CPU cao) trong khi hệ thống vẫn tự co giãn hoặc tự hồi phục, kỹ sư sẽ bị kiệt sức vì cảnh báo giả (Alert Fatigue) và cuối cùng sẽ bỏ qua những cảnh báo sự cố nghiêm trọng thực sự.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Rob Ewaschuk: My Philosophy on Alerting (Google SRE, https://sre.google/sre-book/monitoring-distributed-systems/#alerting-philosophy)</t>
         </is>
       </c>
     </row>
@@ -1216,10 +1319,36 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Condition/duration, Severity.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Condition/duration, Severity.</t>
+- 1.0đ: Thiết kế payload cảnh báo chuyên nghiệp với đầy đủ summary, severity, SLI hiện tại, và phạm vi tác động.
+- 1.0đ: Tích hợp đầy đủ các liên kết hữu ích (runbook_url, deep links sang Grafana dashboard và Tempo trace waterfall).
+- 1.0đ: Thiết kế các bước can thiệp khẩn cấp tức thì (fallback provider, traffic shedding) có thể dập tắt sự cố trong vài phút.
+- 1.0đ: Xác định tiêu chí kiểm chứng phục hồi đưa burn rate về mức an toàn sau hành động.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hợp đồng Cảnh báo Hành động được (Actionable Alert Contract) và Runbook cho Sự cố SLO Burn trên route `/chat`:
+1. **Cấu trúc Alert Payload Chuẩn hóa (PagerDuty / Alertmanager Payload)**:
+```yaml
+alert: ChatServiceHighErrorBudgetBurnRate
+severity: CRITICAL
+service: chat-service
+route: /chat
+tier: enterprise
+summary: "Route /chat dành cho khách hàng Enterprise đang đốt cháy Error Budget với tốc độ 14.4x (tiêu thụ 2% budget trong 1 giờ)."
+sli_current: "Error rate hiện tại: 7.2% (Ngưỡng SLO cam kết: 99.5% success, tức max error 0.5%)."
+impact: "Ước tính khoảng 1.200 người dùng Enterprise đang gặp lỗi HTTP 500 hoặc timeout."
+runbook_url: "https://wiki.internal/ops/runbooks/chat-enterprise-slo-burn"
+correlated_links:
+  grafana: "https://grafana.internal/d/chat-sre?var-tenant_tier=enterprise"
+  tempo_traces: "https://tempo.internal/explore?query={service.name='chat-service' &amp;&amp; status=error}"
+```
+2. **Hợp đồng Runbook Hành động Ngay (Immediate Runbook Contract - 4 Bước Tiêu chuẩn)**:
+- **Bước 1: Triage 2 phút (Phân loại nhanh)**: Mở link Grafana đi kèm, xác định lỗi tập trung ở model provider bên ngoài (OpenAI/Anthropic) hay cụm inference nội bộ.
+- **Bước 2: Giảm tải / Khắc phục khẩn (Immediate Mitigation)**: Nếu nhà cung cấp chính gặp sự cố, kích hoạt cờ fallback `FALLBACK_MODEL_PROVIDER=secondary` để chuyển lưu lượng sang model dự phòng.
+- **Bước 3: Ngắt tải phụ (Shed Low-priority Load)**: Kích hoạt circuit breaker ngắt bớt các tính năng phụ trợ (như streaming format, rich styling) để ưu tiên trả text thuần cho route chat.
+- **Bước 4: Xác nhận phục hồi (Recovery Verification)**: Quan sát burn rate trên Grafana trở về dưới 1x trong 10 phút sau khi thực hiện can thiệp.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một cảnh báo không thể hành động (unactionable alert) chỉ là một tiếng chuông báo thức gây hoang mang. Một Actionable Alert Contract phải trả lời ngay 4 câu hỏi: Chuyện gì đang xảy ra? Mức độ nghiêm trọng ra sao? Runbook nằm ở đâu? và Có link chẩn đoán trực tiếp không? Runbook đi kèm phải cung cấp các bước can thiệp khẩn cấp (mitigation) dứt khoát trong vòng vài phút thay vì hướng dẫn đọc lý thuyết.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Workbook: Alerting on SLOs (https://sre.google/workbook/alerting-on-slos/) &amp; PagerDuty Incident Response Documentation</t>
         </is>
       </c>
     </row>
@@ -1298,10 +1427,22 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Page, Warning.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Page, Warning.</t>
+- 1.0đ: Định tuyến chuẩn xác Critical SLO burn sang PagerDuty gọi điện khẩn cho on-call.
+- 1.0đ: Định tuyến chuẩn xác Warning Disk Trend sang Slack/Jira xử lý giờ hành chính, không gây thức giấc vô ích.
+- 1.0đ: Cấu hình cơ chế Gom nhóm (Alert Grouping theo service/alertname) triệt tiêu tiếng ồn từ 3 replicas.
+- 1.0đ: Thiết lập quy tắc Ức chế cảnh báo (Alert Inhibition) ngăn chặn bão cảnh báo phụ thuộc khi hạ tầng gốc gặp sự cố.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hệ thống Định tuyến Cảnh báo và Kiểm soát Kiệt sức (Alert Routing &amp; Fatigue Control):
+1. **Định tuyến Phân tầng theo Mức độ Nghiêm trọng (Tiered Routing Matrix)**:
+- **Critical SLO Burn Rate Alert**: Định tuyến tới **PagerDuty (Gọi điện/SMS khẩn cấp 24/7)** cho kỹ sư trực chiến on-call. Yêu cầu phản hồi (ACK) trong vòng 10 phút. Lý do: Đây là sự cố trực tiếp đe dọa cam kết khách hàng và ngân sách lỗi.
+- **Warning Disk Trend (Dự báo đầy đĩa sau vài ngày)**: Định tuyến tới **Slack channel `#ops-warnings`** hoặc tự động mở **Ticket Jira có độ ưu tiên Medium**. Không gọi điện PagerDuty làm gián đoạn giấc ngủ hay công việc của kỹ sư. Lý do: Sự cố có nhiều ngày để xử lý trong giờ hành chính.
+2. **Kiểm soát Cảnh báo Trùng lặp từ Ba Replicas (Deduplication, Grouping &amp; Inhibition)**:
+- **Alert Grouping (Gom nhóm)**: Cấu hình Alertmanager gom các cảnh báo có cùng bộ nhãn: `group_by: ['alertname', 'cluster', 'service']`. Cài đặt `group_wait: 30s` và `group_interval: 5m`. Khi 3 replicas cùng bắn cảnh báo lỗi, Alertmanager sẽ gộp lại thành đúng 1 thông báo duy nhất hiển thị '3 instances impacted' thay vì gửi 3 thông báo rác riêng lẻ.
+- **Alert Inhibition (Ức chế cảnh báo phụ thuộc)**: Thiết lập quy tắc: nếu cảnh báo cấp cao `ClusterNetworkDown` đang kích hoạt, tự động ức chế (tắt chuông) toàn bộ các cảnh báo cấp thấp hơn như `InstanceUnreachable` hay `ServiceHTTP5xx` xuất phát từ cluster đó để tránh hiện tượng bão thông báo (alert storm).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kiệt sức vì cảnh báo (Alert Fatigue) là kẻ thù số một của an toàn vận hành: khi nhận quá nhiều thông báo trùng lặp hoặc không khẩn cấp, con người có xu hướng phớt lờ toàn bộ các cảnh báo, dẫn đến việc bỏ sót sự cố chí mạng. Hệ thống định tuyến chuẩn mực của Prometheus Alertmanager giải quyết triệt để vấn đề này thông qua cơ chế Grouping (gom cụm replica), Inhibition (ức chế cảnh báo thứ cấp), và phân luồng kênh nhận (PagerDuty cho sự cố khẩn vs Slack/Jira cho cảnh báo phòng ngừa).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Prometheus Alertmanager Configuration: Grouping and Inhibition (https://prometheus.io/docs/alerting/latest/configuration/) &amp; Google SRE Book</t>
         </is>
       </c>
     </row>
@@ -1384,10 +1525,29 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Good/eligible event, Population/scope.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Good/eligible event, Population/scope.</t>
+- 1.0đ: Định nghĩa chuẩn xác SLI với công thức toán học đo lường định lượng tỷ lệ request thành công.
+- 1.0đ: Định nghĩa chuẩn xác SLO mục tiêu nội bộ (99.5%) kèm quy tắc chính sách Error Budget (feature freeze).
+- 1.0đ: Định nghĩa chuẩn xác SLA pháp lý (99.0%) kèm chế tài hoàn tiền/service credit cụ thể.
+- 1.0đ: Giải thích rõ lý do vì sao SLO phải khắt khe hơn SLA để tạo vùng đệm an toàn tài chính.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết lập Ba Bản Hợp đồng Phân định Rạch ròi: SLI, SLO và SLA (Tuyệt đối không trộn lẫn):
+1. **SLI (Service Level Indicator - Chỉ số Đo lường Kỹ thuật Thực tế)**:
+- **Bản chất**: Thước đo định lượng chính xác xem dịch vụ đang hoạt động như thế nào tại một thời điểm hoặc khoảng thời gian.
+- **Công thức toán học cụ thể**:
+  $$\text{SLI}_{\text{availability}} = \frac{\sum \text{HTTP Requests hợp lệ trả về status } &lt; 500}{\sum \text{Tổng số HTTP Requests hợp lệ}} \times 100\%$$
+- Đối tượng: Dữ liệu kỹ thuật đo được từ telemetry, không chứa mục tiêu hay ràng buộc kinh doanh.
+2. **SLO (Service Level Objective - Mục tiêu Nội bộ và Ngân sách Lỗi)**:
+- **Bản chất**: Mục tiêu kỹ thuật nội bộ mà đội ngũ kỹ thuật cam kết duy trì để bảo đảm người dùng hài lòng, đi kèm Ngân sách lỗi (Error Budget).
+- **Định lượng**: $\text{SLI}_{\text{availability}} \ge 99.5\%$ đo lường trên cửa sổ trượt 30 ngày (rolling 30-day window).
+- **Chính sách Error Budget (0.5% lỗi)**: Nếu Error Budget bị tiêu cạn trong tháng, toàn bộ đội ngũ kỹ thuật phải đóng băng phát triển tính năng mới (feature freeze) để tập trung nâng cấp độ ổn định hạ tầng.
+3. **SLA (Service Level Agreement - Thỏa thuận Hợp đồng Pháp lý &amp; Kinh doanh)**:
+- **Bản chất**: Cam kết pháp lý chính thức giữa nhà cung cấp dịch vụ và khách hàng trả phí, có chế tài bồi thường tài chính khi vi phạm.
+- **Định lượng**: Thường được đặt lỏng hơn SLO nội bộ để tạo vùng đệm an toàn (Safety Buffer), ví dụ: $\text{Availability} \ge 99.0\%$ theo tháng.
+- **Chế tài xử phạt (Financial Penalties)**: Nếu tính khả dụng trong tháng giảm xuống dưới 99.0%, hoàn trả 15% cước phí dịch vụ; nếu dưới 95.0%, hoàn trả 50% cước phí dưới dạng Service Credits.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mối quan hệ tam giác SLI - SLO - SLA là nền tảng của kỹ nghệ SRE: SLI là những gì bạn đo lường; SLO là mục tiêu nội bộ bạn hướng tới; còn SLA là cam kết pháp lý bạn hứa với khách hàng kèm mức phạt tiền. Quy tắc bất biến: SLO luôn luôn phải khắt khe hơn SLA (SLO &gt; SLA). Khoảng cách giữa SLO (99.5%) và SLA (99.0%) chính là biên độ an toàn (safety buffer) giúp đội ngũ kỹ thuật phát hiện và dập tắt sự cố trước khi phải bồi thường tiền cho khách hàng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Service Level Objectives (Chapter 4) &amp; The Site Reliability Workbook: Implementing SLOs</t>
         </is>
       </c>
     </row>
